--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 13:21</t>
+          <t>更新时间: 2026-09-06 16:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-06 16:26</t>
+          <t>更新时间: 2026-09-07 09:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-07 09:14</t>
+          <t>更新时间: 2026-09-08 09:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-08 09:15</t>
+          <t>更新时间: 2026-09-09 09:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-09 09:14</t>
+          <t>更新时间: 2026-09-10 09:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-10 09:14</t>
+          <t>更新时间: 2026-09-11 09:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-11 09:13</t>
+          <t>更新时间: 2026-09-12 09:13</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-12 09:13</t>
+          <t>更新时间: 2026-09-13 09:13</t>
         </is>
       </c>
     </row>
